--- a/シナリオ管理.xlsx
+++ b/シナリオ管理.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="3841" documentId="8_{24A741F6-B34A-40D1-98C6-91A0845EA44A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{897E9874-2D66-4D8D-BD91-569ED4C33CDD}"/>
   <bookViews>
-    <workbookView xWindow="975" yWindow="975" windowWidth="24000" windowHeight="12000" activeTab="3" xr2:uid="{EBBF1870-7AB0-4A89-8A92-C245957E7B93}"/>
+    <workbookView xWindow="2520" yWindow="1860" windowWidth="24000" windowHeight="12000" activeTab="3" xr2:uid="{EBBF1870-7AB0-4A89-8A92-C245957E7B93}"/>
   </bookViews>
   <sheets>
     <sheet name="PathChartTree" sheetId="5" r:id="rId1"/>
@@ -366,35 +366,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
